--- a/artfynd/A 26260-2026 artfynd.xlsx
+++ b/artfynd/A 26260-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121149625</v>
+        <v>121149626</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699043</v>
+        <v>699314</v>
       </c>
       <c r="R2" t="n">
-        <v>7308374</v>
+        <v>7307948</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -783,223 +778,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>121149626</v>
-      </c>
-      <c r="B3" t="n">
-        <v>79717</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tjappsåive, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>699314</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7307948</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>127415054</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91370</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tjappsåive, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>699166</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7308110</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26260-2026 artfynd.xlsx
+++ b/artfynd/A 26260-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938739</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938768</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999438</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938742</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938746</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938722</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938725</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938736</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938754</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938760</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938734</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149626</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2295,6 +2370,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938717</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2411,6 +2491,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938733</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2527,6 +2612,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938737</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2639,6 +2729,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938749</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2751,6 +2846,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938751</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2863,6 +2963,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938759</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938763</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3087,6 +3197,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938769</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3199,6 +3314,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938774</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3315,6 +3435,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938781</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3431,6 +3556,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938783</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3543,6 +3673,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999441</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3655,6 +3790,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999442</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3771,6 +3911,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999443</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3883,6 +4028,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999444</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3999,6 +4149,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999446</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4118,6 +4273,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134999436</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4233,6 +4393,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938756</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4340,6 +4505,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938778</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4447,6 +4617,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938775</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4554,6 +4729,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938740</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4661,8 +4841,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134938766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26260-2026 artfynd.xlsx
+++ b/artfynd/A 26260-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134999448</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134938757</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>134938739</v>
       </c>
       <c r="B4" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>134938768</v>
       </c>
       <c r="B5" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>134999438</v>
       </c>
       <c r="B6" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>134938742</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>134938746</v>
       </c>
       <c r="B8" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>134938722</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>134938725</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>134938736</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>134938754</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>134938760</v>
       </c>
       <c r="B13" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>134938734</v>
       </c>
       <c r="B14" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>134938717</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>134938733</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>134938737</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>134938749</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>134938751</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>134938759</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>134938763</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>134938769</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>134938774</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>134938781</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>134938783</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>134999441</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>134999442</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>134999443</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>134999444</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>134999446</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>134999436</v>
       </c>
       <c r="B32" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>134938756</v>
       </c>
       <c r="B33" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>134938778</v>
       </c>
       <c r="B34" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>134938775</v>
       </c>
       <c r="B35" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>134938740</v>
       </c>
       <c r="B36" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>134938766</v>
       </c>
       <c r="B37" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 26260-2026 artfynd.xlsx
+++ b/artfynd/A 26260-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134999448</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>134999438</v>
       </c>
       <c r="B6" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
